--- a/1316_Cuenca_Locumba/_raw_reportes_xlsx/IDConfig_67724_completo.xlsx
+++ b/1316_Cuenca_Locumba/_raw_reportes_xlsx/IDConfig_67724_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra5e6f27df755460c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R711c8371914d48f5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0086</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9994</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0086</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/1316_Cuenca_Locumba/_raw_reportes_xlsx/IDConfig_67724_completo.xlsx
+++ b/1316_Cuenca_Locumba/_raw_reportes_xlsx/IDConfig_67724_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R711c8371914d48f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re5025a152f9b44bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9994</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9947</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9947</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9994</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9947</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9947</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9994</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9924</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9901</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9994</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9947</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0040</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0040</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0040</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9994</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0040</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9994</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9994</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9994</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0040</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0040</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0040</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0131</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9924</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0086</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0040</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,43 +984,268 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      3.0040</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0086</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9994</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0086</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0086</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0199</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      3.0017</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>22/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0086</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.9994</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/08/2026</x:t>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -315,7 +1260,22 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>19/08/2026</x:t>
+          <x:t>04/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -330,22 +1290,67 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>18/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0086</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/08/2026</x:t>
+          <x:t>02/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0199</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -360,7 +1365,22 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>16/08/2026</x:t>
+          <x:t>28/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -375,7 +1395,22 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>15/08/2026</x:t>
+          <x:t>26/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -390,22 +1425,397 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>14/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0086</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/08/2026</x:t>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0199</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9924</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -420,22 +1830,97 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>12/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0086</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/08/2026</x:t>
+          <x:t>27/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0221</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0176</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -450,67 +1935,112 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>10/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.9971</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.9971</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0017</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/08/2026</x:t>
+          <x:t>20/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0131</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0199</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0199</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0199</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0243</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0288</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -525,97 +2055,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>05/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0108</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0017</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0017</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/07/2026</x:t>
+          <x:t>12/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -630,247 +2070,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>29/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0108</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.9877</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0017</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0108</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0108</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0154</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0154</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0108</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0154</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0154</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/07/2026</x:t>
+          <x:t>11/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -885,367 +2085,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>12/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0154</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0108</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0154</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0017</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.9971</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.9971</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.9924</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.9971</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0154</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0108</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0154</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0040</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0154</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0108</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0221</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0176</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0154</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0131</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0131</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0154</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/06/2026</x:t>
+          <x:t>10/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1260,37 +2100,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>17/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0199</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0199</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/06/2026</x:t>
+          <x:t>09/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1305,7 +2115,67 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>14/06/2026</x:t>
+          <x:t>08/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0243</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0332</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0243</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0243</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1320,97 +2190,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>13/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0108</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0199</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0199</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0199</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0243</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0243</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/06/2026</x:t>
+          <x:t>03/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1425,37 +2205,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>06/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0243</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0243</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/06/2026</x:t>
+          <x:t>02/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1470,7 +2220,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>03/06/2026</x:t>
+          <x:t>01/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1485,22 +2235,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>02/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0288</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/06/2026</x:t>
+          <x:t>31/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1515,7 +2250,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>31/05/2026</x:t>
+          <x:t>30/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1530,7 +2265,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>30/05/2026</x:t>
+          <x:t>29/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1545,21 +2280,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>29/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0332</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>28/05/2026</x:t>
         </x:is>
       </x:c>
@@ -1599,7 +2319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0154</x:v>
+        <x:v>      3.0376</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1614,7 +2334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0288</x:v>
+        <x:v>      3.0419</x:v>
       </x:c>
     </x:row>
     <x:row>
